--- a/prius2/input/criterium_impact_v26-01-26.xlsx
+++ b/prius2/input/criterium_impact_v26-01-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bram_dhondt\Documents\GitHub\prius\prius2\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF71810-2AC0-4738-A62C-7F1B4D6B7DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA478457-8F2C-4464-9350-78199CF34494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="300">
   <si>
     <t>soort</t>
   </si>
@@ -943,11 +943,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1054,17 +1061,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1073,45 +1077,56 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1119,49 +1134,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFEF2CB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFEF2CB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFEF2CB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1376,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:O1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
@@ -1971,13 +1943,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="1">
         <v>5871429</v>
       </c>
       <c r="D21" s="10" t="s">
@@ -2318,32 +2290,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="19" t="s">
+    <row r="33" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="21">
         <v>8114276</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="E33" s="21">
-        <v>1</v>
-      </c>
-      <c r="F33" s="21">
-        <v>0</v>
-      </c>
-      <c r="G33" s="21">
-        <v>0</v>
-      </c>
-      <c r="H33" s="21">
-        <v>0</v>
-      </c>
-      <c r="I33" s="21">
+      <c r="E33" s="23">
+        <v>1</v>
+      </c>
+      <c r="F33" s="23">
+        <v>0</v>
+      </c>
+      <c r="G33" s="23">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23">
+        <v>0</v>
+      </c>
+      <c r="I33" s="23">
         <v>0</v>
       </c>
     </row>
@@ -2360,8 +2332,8 @@
       <c r="D34" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>9</v>
+      <c r="E34" s="13">
+        <v>1</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
@@ -2372,8 +2344,8 @@
       <c r="H34" s="4">
         <v>0</v>
       </c>
-      <c r="I34" s="5">
-        <v>1</v>
+      <c r="I34" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2430,8 +2402,8 @@
       <c r="H36" s="4">
         <v>0</v>
       </c>
-      <c r="I36" s="4">
-        <v>0</v>
+      <c r="I36" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2447,24 +2419,24 @@
       <c r="D37" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="5">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0</v>
-      </c>
-      <c r="I37" s="5">
-        <v>0</v>
+      <c r="E37" s="17">
+        <v>1</v>
+      </c>
+      <c r="F37" s="16">
+        <v>0</v>
+      </c>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="16">
+        <v>0</v>
+      </c>
+      <c r="I37" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2479,7 +2451,7 @@
       <c r="E38" s="4">
         <v>1</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="16">
         <v>1</v>
       </c>
       <c r="G38" s="4">
@@ -2489,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2534,8 +2506,8 @@
       <c r="D40" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>9</v>
+      <c r="E40" s="13">
+        <v>1</v>
       </c>
       <c r="F40" s="4">
         <v>0</v>
@@ -2543,11 +2515,11 @@
       <c r="G40" s="4">
         <v>0</v>
       </c>
-      <c r="H40" s="4">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4">
-        <v>0</v>
+      <c r="H40" s="13">
+        <v>1</v>
+      </c>
+      <c r="I40" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2621,8 +2593,8 @@
       <c r="D43" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>9</v>
+      <c r="E43" s="13">
+        <v>1</v>
       </c>
       <c r="F43" s="4">
         <v>0</v>
@@ -2679,8 +2651,8 @@
       <c r="D45" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>9</v>
+      <c r="E45" s="13">
+        <v>1</v>
       </c>
       <c r="F45" s="4">
         <v>0</v>
@@ -2691,7 +2663,7 @@
       <c r="H45" s="4">
         <v>1</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="16">
         <v>1</v>
       </c>
     </row>
@@ -2911,11 +2883,11 @@
       <c r="D53" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="5">
-        <v>1</v>
+      <c r="E53" s="13">
+        <v>1</v>
+      </c>
+      <c r="F53" s="16">
+        <v>0</v>
       </c>
       <c r="G53" s="4">
         <v>0</v>
@@ -2923,8 +2895,8 @@
       <c r="H53" s="4">
         <v>0</v>
       </c>
-      <c r="I53" s="4">
-        <v>0</v>
+      <c r="I53" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2940,8 +2912,8 @@
       <c r="D54" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>9</v>
+      <c r="E54" s="13">
+        <v>1</v>
       </c>
       <c r="F54" s="4">
         <v>0</v>
@@ -2952,8 +2924,8 @@
       <c r="H54" s="4">
         <v>0</v>
       </c>
-      <c r="I54" s="5">
-        <v>1</v>
+      <c r="I54" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2972,8 +2944,8 @@
       <c r="E55" s="4">
         <v>1</v>
       </c>
-      <c r="F55" s="4">
-        <v>1</v>
+      <c r="F55" s="13">
+        <v>0</v>
       </c>
       <c r="G55" s="4">
         <v>0</v>
@@ -2981,8 +2953,8 @@
       <c r="H55" s="4">
         <v>0</v>
       </c>
-      <c r="I55" s="5">
-        <v>0</v>
+      <c r="I55" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3085,8 +3057,8 @@
       <c r="D59" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>9</v>
+      <c r="E59" s="13">
+        <v>1</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
@@ -3097,7 +3069,7 @@
       <c r="H59" s="4">
         <v>0</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I59" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3117,8 +3089,8 @@
       <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="F60" s="4">
-        <v>1</v>
+      <c r="F60" s="13">
+        <v>0</v>
       </c>
       <c r="G60" s="4">
         <v>0</v>
@@ -3126,8 +3098,8 @@
       <c r="H60" s="4">
         <v>0</v>
       </c>
-      <c r="I60" s="5">
-        <v>0</v>
+      <c r="I60" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3218,20 +3190,20 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="25">
         <v>3084842</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>9</v>
+      <c r="E64" s="13">
+        <v>1</v>
       </c>
       <c r="F64" s="4">
         <v>0</v>
@@ -3242,36 +3214,36 @@
       <c r="H64" s="4">
         <v>0</v>
       </c>
-      <c r="I64" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+      <c r="I64" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="18">
         <v>2482499</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="E65" s="4">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="4">
-        <v>0</v>
-      </c>
-      <c r="H65" s="4">
-        <v>0</v>
-      </c>
-      <c r="I65" s="4">
+      <c r="E65" s="20">
+        <v>1</v>
+      </c>
+      <c r="F65" s="20">
+        <v>0</v>
+      </c>
+      <c r="G65" s="20">
+        <v>0</v>
+      </c>
+      <c r="H65" s="20">
+        <v>0</v>
+      </c>
+      <c r="I65" s="20">
         <v>0</v>
       </c>
     </row>
@@ -3578,8 +3550,8 @@
       <c r="D76" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>9</v>
+      <c r="E76" s="13">
+        <v>1</v>
       </c>
       <c r="F76" s="4">
         <v>0</v>
@@ -4174,7 +4146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4203,7 +4175,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>212</v>
       </c>
@@ -4232,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>214</v>
       </c>
@@ -4261,7 +4233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>216</v>
       </c>
@@ -4290,7 +4262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>218</v>
       </c>
@@ -4319,7 +4291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>220</v>
       </c>
@@ -4348,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>222</v>
       </c>
@@ -4377,7 +4349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>88</v>
       </c>
@@ -4406,7 +4378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>224</v>
       </c>
@@ -4435,7 +4407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>226</v>
       </c>
@@ -4464,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>90</v>
       </c>
@@ -4493,7 +4465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>92</v>
       </c>
@@ -4506,8 +4478,8 @@
       <c r="D108" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>9</v>
+      <c r="E108" s="13">
+        <v>1</v>
       </c>
       <c r="F108" s="4">
         <v>0</v>
@@ -4521,8 +4493,13 @@
       <c r="I108" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+    </row>
+    <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>228</v>
       </c>
@@ -4551,7 +4528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>230</v>
       </c>
@@ -4580,7 +4557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>93</v>
       </c>
@@ -4609,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>232</v>
       </c>
@@ -5260,8 +5237,8 @@
       <c r="D134" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E134" s="4" t="s">
-        <v>9</v>
+      <c r="E134" s="13">
+        <v>1</v>
       </c>
       <c r="F134" s="4">
         <v>0</v>
@@ -11673,7 +11650,7 @@
     <sortCondition ref="A2:A149"/>
   </sortState>
   <conditionalFormatting sqref="D2:D149">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"ja"</formula>
     </cfRule>
   </conditionalFormatting>
